--- a/excel_routes/route_MED_HBE_threats.xlsx
+++ b/excel_routes/route_MED_HBE_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +50,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -80,6 +92,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -447,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -459,7 +477,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -523,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09-APR-26</t>
+          <t>24-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -533,33 +551,1068 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>flyadeal F3-775</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>489</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>954</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>-465</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>24-MAY-26</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-771</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>489</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>954</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>-465</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>24-MAY-26</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>EgyptAir MS-680</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
-        <v>559</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>520</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="G2" s="2" t="n">
+      <c r="D4" s="2" t="n">
+        <v>1147</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>954</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>193</v>
+      </c>
+      <c r="G4" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H4" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-771</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>419</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>1338</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>-919</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-391</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>1338</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>-909</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-317</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>1338</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>-909</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-381</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>494</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>1338</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>-844</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-315</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>494</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>1338</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>-844</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-680</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>547</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>1338</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>-791</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-676</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>547</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>1338</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>-791</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-694</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>547</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>1338</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>-791</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-640</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>547</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>1338</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>-791</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-678</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>604</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>1338</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>-734</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-793</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>629</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>1338</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>-709</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-576</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>629</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>1338</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>-709</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>31-MAY-26</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-775</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>699</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>1338</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>-639</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>31-MAY-26</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-576</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>799</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>1338</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>-539</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>31-MAY-26</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-771</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>1099</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>1338</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>-239</v>
+      </c>
+      <c r="G19" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="I2" s="2" t="n">
-        <v>-6</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="H19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>07-JUN-26</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-576</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>876</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>-447</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>11-JUN-26</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-793</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>399</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>798</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>-399</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>11-JUN-26</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-576</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>399</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>798</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>-399</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>14-JUN-26</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-576</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>399</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>798</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-399</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>21-JUN-26</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-576</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>659</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>798</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>-139</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>21-JUN-26</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-680</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>897</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>798</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_MED_HBE_threats.xlsx
+++ b/excel_routes/route_MED_HBE_threats.xlsx
@@ -48,6 +48,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
       </patternFill>
@@ -56,12 +62,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F8D7DA"/>
         <bgColor rgb="00F8D7DA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>16-APR-26</t>
+          <t>24-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,30 +551,30 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>729</v>
+        <v>923</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>798</v>
+        <v>1150</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-69</v>
+        <v>-227</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>16-APR-26</t>
+          <t>24-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,30 +596,30 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>729</v>
+        <v>931</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>798</v>
+        <v>1150</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-69</v>
+        <v>-219</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>24-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,17 +641,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-391</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>775</v>
+        <v>980</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>798</v>
+        <v>1150</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-23</v>
+        <v>-170</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>46</v>
@@ -664,7 +664,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>24-MAY-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,17 +686,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-317</t>
+          <t>EgyptAir MS-680</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>775</v>
+        <v>1048</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>798</v>
+        <v>1150</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-23</v>
+        <v>-102</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>46</v>
@@ -709,7 +709,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>24-MAY-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,28 +731,28 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>489</v>
+        <v>789</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>954</v>
+        <v>1054</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-465</v>
+        <v>-265</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>24-MAY-26</t>
+          <t>05-JUL-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,28 +776,28 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>489</v>
+        <v>833</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>954</v>
+        <v>976</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-465</v>
+        <v>-143</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>24-MAY-26</t>
+          <t>05-JUL-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,17 +821,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-680</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1147</v>
+        <v>833</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>954</v>
+        <v>976</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>193</v>
+        <v>-143</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>46</v>
@@ -842,7 +842,7 @@
       <c r="I8" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>28-MAY-26</t>
+          <t>05-JUL-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,30 +866,30 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>419</v>
+        <v>833</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1338</v>
+        <v>976</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-919</v>
+        <v>-143</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>28-MAY-26</t>
+          <t>05-JUL-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,30 +911,30 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-391</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>429</v>
+        <v>833</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1338</v>
+        <v>976</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-909</v>
+        <v>-143</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>-16</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>28-MAY-26</t>
+          <t>05-JUL-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,28 +956,28 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-317</t>
+          <t>EgyptAir MS-680</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>429</v>
+        <v>848</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1338</v>
+        <v>976</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-909</v>
+        <v>-128</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>MEDIUM THREAT - MONITOR</t>
         </is>
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>28-MAY-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,30 +1001,30 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>494</v>
+        <v>753</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1338</v>
+        <v>976</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-844</v>
+        <v>-223</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>30</v>
+        <v>-16</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>28-MAY-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,30 +1046,30 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-315</t>
+          <t>EgyptAir MS-680</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>494</v>
+        <v>778</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1338</v>
+        <v>976</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-844</v>
+        <v>-198</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>-16</v>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>28-MAY-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,30 +1091,30 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-680</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>547</v>
+        <v>826</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1338</v>
+        <v>976</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-791</v>
+        <v>-150</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>7</v>
+        <v>-10</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>28-MAY-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,30 +1136,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>547</v>
+        <v>826</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1338</v>
+        <v>976</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-791</v>
+        <v>-150</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>7</v>
+        <v>-10</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>28-MAY-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,30 +1181,30 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>547</v>
+        <v>833</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1338</v>
+        <v>976</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-791</v>
+        <v>-143</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>28-MAY-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1230,26 +1230,26 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>547</v>
+        <v>833</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1338</v>
+        <v>976</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-791</v>
+        <v>-143</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>28-MAY-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,30 +1271,30 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>604</v>
+        <v>906</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1338</v>
+        <v>976</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-734</v>
+        <v>-70</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>7</v>
+        <v>-10</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>28-MAY-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,30 +1316,30 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>629</v>
+        <v>906</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1338</v>
+        <v>976</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-709</v>
+        <v>-70</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>-10</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>28-MAY-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,30 +1361,30 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>629</v>
+        <v>923</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1338</v>
+        <v>976</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-709</v>
+        <v>-53</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J20" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>-16</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,30 +1406,30 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-680</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>895</v>
+        <v>698</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1338</v>
+        <v>976</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-443</v>
+        <v>-278</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>7</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>989</v>
+        <v>799</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1338</v>
+        <v>976</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-349</v>
+        <v>-177</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>40</v>
@@ -1472,9 +1472,9 @@
       <c r="I22" s="2" t="n">
         <v>-10</v>
       </c>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1500,13 +1500,13 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>1099</v>
+        <v>826</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>1338</v>
+        <v>976</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-239</v>
+        <v>-150</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>40</v>
@@ -1517,7 +1517,7 @@
       <c r="I23" s="2" t="n">
         <v>-10</v>
       </c>
-      <c r="J23" s="3" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,28 +1541,28 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>899</v>
+        <v>833</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1338</v>
+        <v>976</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-439</v>
+        <v>-143</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,28 +1586,28 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>429</v>
+        <v>903</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>876</v>
+        <v>976</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-447</v>
+        <v>-73</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1631,28 +1631,28 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>799</v>
+        <v>903</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>876</v>
+        <v>976</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-77</v>
+        <v>-73</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>11-JUN-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,28 +1676,28 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>399</v>
+        <v>906</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>798</v>
+        <v>976</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-399</v>
+        <v>-70</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>11-JUN-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,28 +1721,28 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>798</v>
+        <v>898</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-399</v>
+        <v>-479</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>14-JUN-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1766,28 +1766,28 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>589</v>
+        <v>596</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>798</v>
+        <v>898</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-209</v>
+        <v>-302</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>14-JUN-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,30 +1811,30 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-391</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>698</v>
+        <v>646</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>798</v>
+        <v>898</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-100</v>
+        <v>-252</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>21-JUN-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1860,13 +1860,13 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>659</v>
+        <v>646</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>798</v>
+        <v>898</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-139</v>
+        <v>-252</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>40</v>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>21-JUN-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1905,13 +1905,13 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>897</v>
+        <v>933</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>798</v>
+        <v>898</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>99</v>
+        <v>35</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>46</v>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">

--- a/excel_routes/route_MED_HBE_threats.xlsx
+++ b/excel_routes/route_MED_HBE_threats.xlsx
@@ -477,7 +477,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -574,7 +574,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">

--- a/excel_routes/route_MED_HBE_threats.xlsx
+++ b/excel_routes/route_MED_HBE_threats.xlsx
@@ -48,6 +48,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFF3CD"/>
         <bgColor rgb="00FFF3CD"/>
       </patternFill>
@@ -56,12 +62,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -555,13 +555,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>923</v>
+        <v>753</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1150</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-227</v>
+        <v>-397</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>46</v>
@@ -574,7 +574,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -600,13 +600,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>931</v>
+        <v>761</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1150</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-219</v>
+        <v>-389</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>46</v>
@@ -619,7 +619,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -645,13 +645,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>980</v>
+        <v>810</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1150</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-170</v>
+        <v>-340</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>46</v>
@@ -662,7 +662,7 @@
       <c r="I4" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -686,30 +686,30 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-680</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1048</v>
+        <v>1026</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1150</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-102</v>
+        <v>-124</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>24-MAY-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,28 +731,28 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>789</v>
+        <v>1026</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1054</v>
+        <v>1150</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-265</v>
+        <v>-124</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>05-JUL-26</t>
+          <t>24-MAY-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,17 +776,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-680</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>833</v>
+        <v>1048</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>976</v>
+        <v>1150</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-143</v>
+        <v>-102</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>46</v>
@@ -799,7 +799,7 @@
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>05-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,30 +821,30 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>833</v>
+        <v>799</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>976</v>
+        <v>1054</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-143</v>
+        <v>-255</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>05-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,28 +866,28 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>833</v>
+        <v>906</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>976</v>
+        <v>1054</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-143</v>
+        <v>-148</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -911,17 +911,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>833</v>
+        <v>810</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-143</v>
+        <v>-166</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>46</v>
@@ -934,7 +934,7 @@
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -956,17 +956,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-680</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>848</v>
+        <v>833</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-128</v>
+        <v>-143</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>46</v>
@@ -977,9 +977,9 @@
       <c r="I11" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>05-JUL-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>753</v>
+        <v>833</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-223</v>
+        <v>-143</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>46</v>
@@ -1022,9 +1022,9 @@
       <c r="I12" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>05-JUL-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-680</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>778</v>
+        <v>833</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-198</v>
+        <v>-143</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>46</v>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>05-JUL-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,28 +1091,28 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>826</v>
+        <v>833</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-150</v>
+        <v>-143</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>05-JUL-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,30 +1136,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-680</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>826</v>
+        <v>848</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-150</v>
+        <v>-128</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>833</v>
+        <v>753</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-143</v>
+        <v>-223</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>46</v>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
@@ -1247,7 +1247,7 @@
       <c r="I17" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1271,28 +1271,28 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>906</v>
+        <v>833</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-70</v>
+        <v>-143</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1316,28 +1316,28 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>906</v>
+        <v>923</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-70</v>
+        <v>-53</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-680</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>923</v>
+        <v>933</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-53</v>
+        <v>-43</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>46</v>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       <c r="I21" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1451,28 +1451,28 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>799</v>
+        <v>833</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-177</v>
+        <v>-143</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1496,28 +1496,28 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>826</v>
+        <v>903</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-150</v>
+        <v>-73</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>12-JUL-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,28 +1541,28 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>833</v>
+        <v>419</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>976</v>
+        <v>898</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-143</v>
+        <v>-479</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>12-JUL-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,28 +1586,28 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>903</v>
+        <v>419</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>976</v>
+        <v>898</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-73</v>
+        <v>-479</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>12-JUL-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1631,28 +1631,28 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>903</v>
+        <v>529</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>976</v>
+        <v>898</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-73</v>
+        <v>-369</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>12-JUL-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1680,24 +1680,24 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>906</v>
+        <v>529</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>976</v>
+        <v>898</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-70</v>
+        <v>-369</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1721,213 +1721,33 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-680</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>419</v>
+        <v>933</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-479</v>
+        <v>35</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>SM-486</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-771</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>596</v>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>-302</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>SM-486</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-793</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>646</v>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>-252</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>SM-486</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-576</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="n">
-        <v>646</v>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>-252</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>SM-486</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-680</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v>933</v>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_MED_HBE_threats.xlsx
+++ b/excel_routes/route_MED_HBE_threats.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -551,17 +551,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>753</v>
+        <v>761</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1150</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-397</v>
+        <v>-389</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>46</v>
@@ -596,17 +596,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>761</v>
+        <v>810</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1150</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-389</v>
+        <v>-340</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>46</v>
@@ -617,9 +617,9 @@
       <c r="I3" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -641,17 +641,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>810</v>
+        <v>833</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1150</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-340</v>
+        <v>-317</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>46</v>
@@ -690,22 +690,22 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1026</v>
+        <v>909</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1150</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-124</v>
+        <v>-241</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
@@ -735,22 +735,22 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1026</v>
+        <v>909</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1150</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-124</v>
+        <v>-241</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
@@ -825,26 +825,26 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>799</v>
+        <v>619</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1054</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-255</v>
+        <v>-435</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>906</v>
+        <v>789</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1054</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-148</v>
+        <v>-265</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
@@ -911,17 +911,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>810</v>
+        <v>833</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-166</v>
+        <v>-143</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>46</v>
@@ -932,9 +932,9 @@
       <c r="I10" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-680</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>833</v>
+        <v>848</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-143</v>
+        <v>-128</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>46</v>
@@ -1112,9 +1112,9 @@
       <c r="I14" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>05-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,17 +1136,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-680</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>848</v>
+        <v>753</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-128</v>
+        <v>-223</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>46</v>
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-680</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>753</v>
+        <v>778</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-223</v>
+        <v>-198</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>46</v>
@@ -1202,9 +1202,9 @@
       <c r="I16" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1365,26 +1365,26 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>933</v>
+        <v>698</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-43</v>
+        <v>-278</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1406,30 +1406,30 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-680</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>698</v>
+        <v>753</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-278</v>
+        <v>-223</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>12-JUL-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>EgyptAir MS-680</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>903</v>
+        <v>933</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>976</v>
+        <v>898</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-73</v>
+        <v>35</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>46</v>
@@ -1517,237 +1517,12 @@
       <c r="I23" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>SM-486</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-775</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>419</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>-479</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J24" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>SM-486</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-771</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>419</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>-479</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>SM-486</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-793</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>529</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>-369</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>SM-486</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-576</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>529</v>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>-369</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>SM-486</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-680</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>933</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_MED_HBE_threats.xlsx
+++ b/excel_routes/route_MED_HBE_threats.xlsx
@@ -48,8 +48,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -60,8 +60,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -477,7 +477,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>24-MAY-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,30 +551,30 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>761</v>
+        <v>909</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1150</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-389</v>
+        <v>-241</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>24-MAY-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,30 +596,30 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>810</v>
+        <v>559</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1150</v>
+        <v>1054</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-340</v>
+        <v>-495</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>24-MAY-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,30 +641,30 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>833</v>
+        <v>619</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1150</v>
+        <v>1054</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-317</v>
+        <v>-435</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>24-MAY-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -690,13 +690,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>909</v>
+        <v>639</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1150</v>
+        <v>1054</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-241</v>
+        <v>-415</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -707,9 +707,9 @@
       <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>24-MAY-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -735,13 +735,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>909</v>
+        <v>719</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1150</v>
+        <v>1054</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-241</v>
+        <v>-335</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -752,9 +752,9 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>24-MAY-26</t>
+          <t>05-JUL-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,17 +776,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-680</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1048</v>
+        <v>833</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1150</v>
+        <v>976</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-102</v>
+        <v>-143</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>46</v>
@@ -797,9 +797,9 @@
       <c r="I7" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>05-JUL-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,30 +821,30 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>619</v>
+        <v>833</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1054</v>
+        <v>976</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-435</v>
+        <v>-143</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>05-JUL-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,30 +866,30 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>789</v>
+        <v>833</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1054</v>
+        <v>976</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-265</v>
+        <v>-143</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
@@ -932,9 +932,9 @@
       <c r="I10" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -956,17 +956,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-680</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>833</v>
+        <v>1048</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-143</v>
+        <v>72</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>46</v>
@@ -977,9 +977,9 @@
       <c r="I11" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>05-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,30 +1001,30 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>833</v>
+        <v>489</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-143</v>
+        <v>-487</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>05-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,30 +1046,30 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>833</v>
+        <v>489</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-143</v>
+        <v>-487</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>05-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,30 +1091,30 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-680</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>848</v>
+        <v>599</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-128</v>
+        <v>-377</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1136,30 +1136,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>753</v>
+        <v>599</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-223</v>
+        <v>-377</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-680</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>778</v>
+        <v>753</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-198</v>
+        <v>-223</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>46</v>
@@ -1202,9 +1202,9 @@
       <c r="I16" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1226,17 +1226,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-680</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>833</v>
+        <v>778</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-143</v>
+        <v>-198</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>46</v>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
@@ -1292,9 +1292,9 @@
       <c r="I18" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>923</v>
+        <v>833</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-53</v>
+        <v>-143</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>46</v>
@@ -1337,9 +1337,9 @@
       <c r="I19" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>12-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,30 +1361,30 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-680</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>698</v>
+        <v>923</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-278</v>
+        <v>-53</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J20" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1406,30 +1406,30 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-680</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>753</v>
+        <v>698</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-223</v>
+        <v>-278</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>833</v>
+        <v>753</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-143</v>
+        <v>-223</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>46</v>
@@ -1472,9 +1472,9 @@
       <c r="I22" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-680</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>933</v>
+        <v>833</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>898</v>
+        <v>976</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>35</v>
+        <v>-143</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>46</v>
@@ -1517,12 +1517,57 @@
       <c r="I23" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-680</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>933</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_MED_HBE_threats.xlsx
+++ b/excel_routes/route_MED_HBE_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +50,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -80,6 +86,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -447,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -523,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -533,26 +542,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1026</v>
+        <v>509</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1150</v>
+        <v>1054</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-124</v>
+        <v>-545</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -568,7 +577,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -578,26 +587,26 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1093</v>
+        <v>539</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1150</v>
+        <v>1054</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-57</v>
+        <v>-515</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -613,7 +622,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -623,33 +632,573 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-315</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1175</v>
+        <v>579</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1150</v>
+        <v>1054</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>25</v>
+        <v>-475</v>
       </c>
       <c r="G4" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>05-JUL-26</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-771</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>469</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>-507</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>05-JUL-26</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-576</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>499</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>-477</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>09-JUL-26</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-696</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>753</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>-223</v>
+      </c>
+      <c r="G7" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="H4" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I4" s="2" t="n">
+      <c r="H7" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I7" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>09-JUL-26</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-676</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>-143</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>09-JUL-26</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-640</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>-143</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>09-JUL-26</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-680</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>848</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>-128</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>12-JUL-26</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-680</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>698</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>-278</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>12-JUL-26</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-694</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>-143</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-793</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>-469</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-576</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>-469</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-775</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>439</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>-459</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-680</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>933</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_MED_HBE_threats.xlsx
+++ b/excel_routes/route_MED_HBE_threats.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -636,22 +636,22 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>579</v>
+        <v>819</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1054</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-475</v>
+        <v>-235</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>15</v>
+        <v>-10</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -947,26 +947,26 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-680</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>698</v>
+        <v>439</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-278</v>
+        <v>-537</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -992,26 +992,26 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>833</v>
+        <v>469</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-143</v>
+        <v>-507</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1037,26 +1037,26 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>EgyptAir MS-680</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>429</v>
+        <v>698</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>898</v>
+        <v>976</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-469</v>
+        <v>-278</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1082,26 +1082,26 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>429</v>
+        <v>833</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>898</v>
+        <v>976</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-469</v>
+        <v>-143</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>439</v>
+        <v>616</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-459</v>
+        <v>-282</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1172,33 +1172,123 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-680</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>933</v>
+        <v>619</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F16" s="2" t="n">
+        <v>-279</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-576</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>619</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>-279</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-680</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>933</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F18" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="G16" s="2" t="n">
+      <c r="G18" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="H16" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I16" s="2" t="n">
+      <c r="H18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_MED_HBE_threats.xlsx
+++ b/excel_routes/route_MED_HBE_threats.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -532,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>28-JUN-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -546,22 +546,22 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>509</v>
+        <v>819</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1054</v>
+        <v>898</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-545</v>
+        <v>-79</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>15</v>
+        <v>-10</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -587,17 +587,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>539</v>
+        <v>509</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1054</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-515</v>
+        <v>-545</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>15</v>
@@ -632,26 +632,26 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>819</v>
+        <v>539</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1054</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-235</v>
+        <v>-515</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>05-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -677,17 +677,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>469</v>
+        <v>579</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>976</v>
+        <v>1054</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-507</v>
+        <v>-475</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>15</v>
@@ -722,17 +722,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>499</v>
+        <v>469</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-477</v>
+        <v>-507</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>15</v>
@@ -757,7 +757,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>05-JUL-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -767,30 +767,30 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>753</v>
+        <v>499</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-223</v>
+        <v>-477</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>05-JUL-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -812,26 +812,26 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>833</v>
+        <v>819</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-143</v>
+        <v>-157</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -857,17 +857,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>833</v>
+        <v>753</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-143</v>
+        <v>-223</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>46</v>
@@ -878,9 +878,9 @@
       <c r="I9" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-680</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>848</v>
+        <v>833</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-128</v>
+        <v>-143</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>46</v>
@@ -923,9 +923,9 @@
       <c r="I10" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>12-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -947,26 +947,26 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>439</v>
+        <v>833</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-537</v>
+        <v>-143</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>12-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -992,30 +992,30 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-680</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>469</v>
+        <v>848</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-507</v>
+        <v>-128</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1037,26 +1037,26 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-680</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>698</v>
+        <v>439</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-278</v>
+        <v>-537</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1082,30 +1082,30 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>833</v>
+        <v>689</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-143</v>
+        <v>-287</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-10</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1117,7 +1117,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1127,26 +1127,26 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-680</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>616</v>
+        <v>698</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>898</v>
+        <v>976</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-282</v>
+        <v>-278</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1172,30 +1172,30 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>619</v>
+        <v>833</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>898</v>
+        <v>976</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-279</v>
+        <v>-143</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1217,30 +1217,30 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>619</v>
+        <v>429</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-279</v>
+        <v>-469</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1262,33 +1262,123 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-680</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>933</v>
+        <v>429</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F18" s="2" t="n">
+        <v>-469</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-775</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>439</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>-459</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-680</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>933</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F20" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="G18" s="2" t="n">
+      <c r="G20" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="H18" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I18" s="2" t="n">
+      <c r="H20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_MED_HBE_threats.xlsx
+++ b/excel_routes/route_MED_HBE_threats.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -532,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>28-JUN-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -542,26 +542,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>819</v>
+        <v>579</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>898</v>
+        <v>1054</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-79</v>
+        <v>-475</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -587,30 +587,30 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>509</v>
+        <v>729</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1054</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-545</v>
+        <v>-325</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-10</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -632,26 +632,26 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>539</v>
+        <v>819</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1054</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-515</v>
+        <v>-235</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>15</v>
+        <v>-10</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>05-JUL-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -677,17 +677,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>579</v>
+        <v>469</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1054</v>
+        <v>976</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-475</v>
+        <v>-507</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>15</v>
@@ -722,17 +722,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-507</v>
+        <v>-477</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>15</v>
@@ -757,7 +757,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>05-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -767,30 +767,30 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>499</v>
+        <v>753</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-477</v>
+        <v>-223</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>05-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -812,26 +812,26 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>819</v>
+        <v>833</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-157</v>
+        <v>-143</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -857,17 +857,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>753</v>
+        <v>833</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-223</v>
+        <v>-143</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>46</v>
@@ -878,9 +878,9 @@
       <c r="I9" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-680</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>833</v>
+        <v>848</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-143</v>
+        <v>-128</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>46</v>
@@ -923,9 +923,9 @@
       <c r="I10" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -947,26 +947,26 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-680</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>833</v>
+        <v>698</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-143</v>
+        <v>-278</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -992,17 +992,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-680</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>848</v>
+        <v>833</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-128</v>
+        <v>-143</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>46</v>
@@ -1013,9 +1013,9 @@
       <c r="I12" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>12-JUL-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1037,17 +1037,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>976</v>
+        <v>898</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-537</v>
+        <v>-469</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>15</v>
@@ -1072,7 +1072,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>12-JUL-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1086,26 +1086,26 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>689</v>
+        <v>429</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>976</v>
+        <v>898</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-287</v>
+        <v>-469</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1117,7 +1117,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>12-JUL-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1127,26 +1127,26 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-680</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>698</v>
+        <v>439</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>976</v>
+        <v>898</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-278</v>
+        <v>-459</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>12-JUL-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1172,17 +1172,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-680</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>833</v>
+        <v>933</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>976</v>
+        <v>898</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-143</v>
+        <v>35</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>46</v>
@@ -1193,192 +1193,12 @@
       <c r="I16" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>SM-486</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-793</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>-469</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>SM-486</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-576</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>-469</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>SM-486</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-775</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>439</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>-459</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>SM-486</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-680</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>933</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_MED_HBE_threats.xlsx
+++ b/excel_routes/route_MED_HBE_threats.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -532,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -542,26 +542,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-680</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>579</v>
+        <v>765</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1054</v>
+        <v>562</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-475</v>
+        <v>203</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -587,30 +587,30 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>729</v>
+        <v>469</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1054</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-325</v>
+        <v>-585</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -632,26 +632,26 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>819</v>
+        <v>619</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1054</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-235</v>
+        <v>-435</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
@@ -757,7 +757,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>05-JUL-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -767,30 +767,30 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>753</v>
+        <v>509</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-223</v>
+        <v>-467</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -812,17 +812,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>833</v>
+        <v>790</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-143</v>
+        <v>-186</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>46</v>
@@ -833,9 +833,9 @@
       <c r="I8" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -857,17 +857,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>833</v>
+        <v>870</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-143</v>
+        <v>-106</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>46</v>
@@ -902,17 +902,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-680</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>848</v>
+        <v>870</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-128</v>
+        <v>-106</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>46</v>
@@ -923,9 +923,9 @@
       <c r="I10" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>12-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -951,26 +951,26 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>698</v>
+        <v>885</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-278</v>
+        <v>-91</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -992,26 +992,26 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>833</v>
+        <v>439</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-143</v>
+        <v>-537</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1037,17 +1037,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>429</v>
+        <v>469</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>898</v>
+        <v>976</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-469</v>
+        <v>-507</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>15</v>
@@ -1072,7 +1072,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1082,26 +1082,26 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-680</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>429</v>
+        <v>735</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>898</v>
+        <v>976</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-469</v>
+        <v>-241</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1127,26 +1127,26 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>439</v>
+        <v>870</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>898</v>
+        <v>976</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-459</v>
+        <v>-106</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1172,33 +1172,168 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-680</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>933</v>
+        <v>429</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>35</v>
+        <v>-469</v>
       </c>
       <c r="G16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-576</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>-469</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-775</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>439</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>-459</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-680</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>970</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="G19" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="H16" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I16" s="2" t="n">
+      <c r="H19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I19" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_MED_HBE_threats.xlsx
+++ b/excel_routes/route_MED_HBE_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -48,14 +48,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF3CD"/>
         <bgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -77,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -89,6 +95,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -456,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -532,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -546,26 +555,26 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>765</v>
+        <v>620</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>562</v>
+        <v>1150</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>203</v>
+        <v>-530</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -587,30 +596,30 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>469</v>
+        <v>620</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1054</v>
+        <v>1150</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-585</v>
+        <v>-530</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -632,30 +641,30 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1054</v>
+        <v>1150</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-435</v>
+        <v>-530</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -667,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>05-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -677,30 +686,30 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>469</v>
+        <v>620</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>976</v>
+        <v>1150</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-507</v>
+        <v>-530</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -726,13 +735,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>499</v>
+        <v>434</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-477</v>
+        <v>-542</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>15</v>
@@ -743,7 +752,7 @@
       <c r="I6" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -767,28 +776,28 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>509</v>
+        <v>620</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-467</v>
+        <v>-356</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -802,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>05-JUL-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -812,30 +821,30 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>790</v>
+        <v>620</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-186</v>
+        <v>-356</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -847,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>05-JUL-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -857,17 +866,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-680</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>870</v>
+        <v>668</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-106</v>
+        <v>-308</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>46</v>
@@ -880,7 +889,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -902,30 +911,30 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-680</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>870</v>
+        <v>620</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>976</v>
+        <v>1054</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-106</v>
+        <v>-434</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -947,30 +956,30 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-680</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>885</v>
+        <v>620</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>976</v>
+        <v>1054</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-91</v>
+        <v>-434</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -982,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>12-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -992,28 +1001,28 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>439</v>
+        <v>620</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>976</v>
+        <v>1054</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-537</v>
+        <v>-434</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1027,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>12-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1037,28 +1046,28 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>469</v>
+        <v>620</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>976</v>
+        <v>1054</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-507</v>
+        <v>-434</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1082,28 +1091,28 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-680</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>735</v>
+        <v>434</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-241</v>
+        <v>-542</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1127,28 +1136,28 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>870</v>
+        <v>439</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-106</v>
+        <v>-537</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1162,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1172,30 +1181,30 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>EgyptAir MS-680</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>429</v>
+        <v>620</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>898</v>
+        <v>976</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-469</v>
+        <v>-356</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1207,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1217,30 +1226,30 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>429</v>
+        <v>701</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>898</v>
+        <v>976</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-469</v>
+        <v>-275</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1252,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1262,28 +1271,28 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>439</v>
+        <v>701</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>898</v>
+        <v>682</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-459</v>
+        <v>19</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1297,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>19-JUL-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1307,17 +1316,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-680</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>970</v>
+        <v>701</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>898</v>
+        <v>682</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>46</v>
@@ -1328,12 +1337,282 @@
       <c r="I19" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>26-JUL-26</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-676</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>653</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>26-JUL-26</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-640</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>653</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-775</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>409</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>-489</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-771</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>409</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-489</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-793</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>434</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>-464</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SM-486</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-680</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>933</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>
